--- a/翻訳表_忍者タイプ診断アプリ.xlsx
+++ b/翻訳表_忍者タイプ診断アプリ.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="385">
   <si>
     <t>画面/コンポーネント</t>
   </si>
@@ -795,154 +795,175 @@
     <t>buke_1</t>
   </si>
   <si>
-    <t>あなたが最も誇りに思うものは?</t>
-  </si>
-  <si>
-    <t>What are you proudest of?</t>
+    <t>忍びとして潜入するなら、どのように?</t>
+  </si>
+  <si>
+    <t>If you were to infiltrate as a shinobi, how would you do it?</t>
   </si>
   <si>
     <t>buke_1a</t>
   </si>
   <si>
-    <t>磨き上げた技術と、それを実際に役立てる力</t>
-  </si>
-  <si>
-    <t>The skill you have honed, and the ability to put it to real use.</t>
+    <t>何度も通い、時間をかけて信頼を得てから中に入る</t>
+  </si>
+  <si>
+    <t>Visit again and again, earning trust over time before stepping inside.</t>
   </si>
   <si>
     <t>buke_1b</t>
   </si>
   <si>
-    <t>深い信念と、人を導く言葉</t>
-  </si>
-  <si>
-    <t>A deep conviction, and words that guide others.</t>
+    <t>物静かに、心を落ち着けたまま歩み入る</t>
+  </si>
+  <si>
+    <t>Walk in quietly, keeping your heart calm and still.</t>
   </si>
   <si>
     <t>buke_1c</t>
   </si>
   <si>
-    <t>積み重ねた知識と、冷静に物事を判断する力</t>
-  </si>
-  <si>
-    <t>The knowledge you have accumulated, and the ability to judge things calmly.</t>
+    <t>相手の様子を見極めながら、慎重に近づく</t>
+  </si>
+  <si>
+    <t>Approach carefully, reading the other person as you go.</t>
+  </si>
+  <si>
+    <t>buke_1d</t>
+  </si>
+  <si>
+    <t>その場の状況に応じて、やり方を柔軟に変える</t>
+  </si>
+  <si>
+    <t>Adapt your approach flexibly to whatever the moment calls for.</t>
   </si>
   <si>
     <t>buke_2</t>
   </si>
   <si>
-    <t>迷いが生じたとき、何を拠り所にする?</t>
-  </si>
-  <si>
-    <t>When you are in doubt, what do you rely on?</t>
+    <t>休みの日をどう過ごしますか?</t>
+  </si>
+  <si>
+    <t>How do you spend your days off?</t>
   </si>
   <si>
     <t>buke_2a</t>
   </si>
   <si>
-    <t>これまで積み重ねてきた経験と、自分の腕</t>
-  </si>
-  <si>
-    <t>The experience you have built up, and your own two hands.</t>
+    <t>決まった相手と、じっくり関係を築く時間に使う</t>
+  </si>
+  <si>
+    <t>Spend the time deepening a relationship with someone you already know well.</t>
   </si>
   <si>
     <t>buke_2b</t>
   </si>
   <si>
-    <t>自分の信じるものと、揺るがぬ信念</t>
-  </si>
-  <si>
-    <t>What you believe in, and an unshakable conviction.</t>
+    <t>静かに過ごし、心を整える時間に充てる</t>
+  </si>
+  <si>
+    <t>Spend it quietly, settling your mind.</t>
   </si>
   <si>
     <t>buke_2c</t>
   </si>
   <si>
-    <t>学んできた知識と、客観的に考える力</t>
-  </si>
-  <si>
-    <t>What you have learned, and the ability to think objectively.</t>
+    <t>本を読んだり、調べ物をして過ごす</t>
+  </si>
+  <si>
+    <t>Spend it reading or looking into things.</t>
+  </si>
+  <si>
+    <t>buke_2d</t>
+  </si>
+  <si>
+    <t>その日の気分で、過ごし方を変える</t>
+  </si>
+  <si>
+    <t>However the mood takes you that day.</t>
   </si>
   <si>
     <t>buke_3</t>
   </si>
   <si>
-    <t>自分の価値を示すとしたら?</t>
-  </si>
-  <si>
-    <t>If you had to demonstrate your own worth, how would you do it?</t>
+    <t>空いた時間に何を究めますか?</t>
+  </si>
+  <si>
+    <t>What do you devote your spare time to mastering?</t>
   </si>
   <si>
     <t>buke_3a</t>
   </si>
   <si>
-    <t>行動と実力で、結果を示す</t>
-  </si>
-  <si>
-    <t>Show it through action and results.</t>
+    <t>人との信頼関係を、じっくり時間をかけて築くこと</t>
+  </si>
+  <si>
+    <t>Building trust with others, slowly and patiently, over time.</t>
   </si>
   <si>
     <t>buke_3b</t>
   </si>
   <si>
-    <t>言葉や生き方で、人に何かを伝える</t>
-  </si>
-  <si>
-    <t>Convey it through your words and how you live.</t>
+    <t>己の内面や、人としての在り方</t>
+  </si>
+  <si>
+    <t>Your own inner self, and what it means to be a person.</t>
   </si>
   <si>
     <t>buke_3c</t>
   </si>
   <si>
-    <t>知識や技術を用いて、人の役に立つ</t>
-  </si>
-  <si>
-    <t>Put your knowledge and skill to use for others.</t>
+    <t>知識や、物事の理屈</t>
+  </si>
+  <si>
+    <t>Knowledge, and the reasoning behind things.</t>
+  </si>
+  <si>
+    <t>buke_3d</t>
+  </si>
+  <si>
+    <t>その時々で、興味のあることを幅広く</t>
+  </si>
+  <si>
+    <t>Whatever happens to interest you at the time, broadly.</t>
   </si>
   <si>
     <t>jisha_1</t>
   </si>
   <si>
-    <t>自分を鍛えるなら、どんな方法を選ぶ?</t>
-  </si>
-  <si>
-    <t>How would you choose to train yourself?</t>
-  </si>
-  <si>
     <t>jisha_1a</t>
   </si>
   <si>
-    <t>人の中に身を置き、自分を律する</t>
-  </si>
-  <si>
-    <t>Place yourself among others, and discipline yourself there.</t>
+    <t>托鉢の僧を装い、里の中に紛れ込む</t>
+  </si>
+  <si>
+    <t>Disguise yourself as a begging monk and slip into the village.</t>
   </si>
   <si>
     <t>jisha_1b</t>
   </si>
   <si>
-    <t>静かな場所で心を整え、己と向き合う</t>
-  </si>
-  <si>
-    <t>Find a quiet place to settle your mind and face yourself.</t>
+    <t>経を唱えながら、寺社の一員として入り込む</t>
+  </si>
+  <si>
+    <t>Chant sutras and enter as one of the temple's own.</t>
   </si>
   <si>
     <t>jisha_1c</t>
   </si>
   <si>
-    <t>厳しい環境に身を置き、己を鍛える</t>
-  </si>
-  <si>
-    <t>Place yourself in a harsh environment and forge yourself through it.</t>
+    <t>山伏の姿で、堂々と山を越えて訪れる</t>
+  </si>
+  <si>
+    <t>Come openly over the mountain, dressed as a yamabushi.</t>
   </si>
   <si>
     <t>jisha_1d</t>
   </si>
   <si>
-    <t>苦しいことから逃げず、最後までやり抜く</t>
-  </si>
-  <si>
-    <t>Never run from hardship, and see it through to the end.</t>
+    <t>法螺貝を吹き鳴らしながら、修行の一団として入り込む</t>
+  </si>
+  <si>
+    <t>Blow the conch-shell horn and enter as part of a band of ascetics.</t>
   </si>
   <si>
     <t>jisha_2</t>
@@ -957,16 +978,16 @@
     <t>jisha_2a</t>
   </si>
   <si>
-    <t>静かに自分の心と向き合う</t>
-  </si>
-  <si>
-    <t>Quietly face your own heart.</t>
+    <t>静かに読経し、自分の心と向き合う</t>
+  </si>
+  <si>
+    <t>Quietly chant a sutra and face your own heart.</t>
   </si>
   <si>
     <t>jisha_2b</t>
   </si>
   <si>
-    <t>人の苦しみや自分の役割を思い返す</t>
+    <t>人々の苦しみと、己の役目を思い返す</t>
   </si>
   <si>
     <t>Recall the suffering of others, and your own purpose.</t>
@@ -975,118 +996,112 @@
     <t>jisha_2c</t>
   </si>
   <si>
-    <t>呼吸を整え、身体の感覚に意識を集中する</t>
-  </si>
-  <si>
-    <t>Steady your breathing and focus on the sensations of your body.</t>
+    <t>法螺貝を吹き鳴らし、呼吸を整える</t>
+  </si>
+  <si>
+    <t>Blow the conch-shell horn and steady your breathing.</t>
   </si>
   <si>
     <t>jisha_2d</t>
   </si>
   <si>
-    <t>あえて厳しい環境に身を置き、自分を奮い立たせる</t>
-  </si>
-  <si>
-    <t>Deliberately place yourself in a harsh environment to spur yourself on.</t>
+    <t>あえて厳しい山に分け入り、自分を奮い立たせる</t>
+  </si>
+  <si>
+    <t>Deliberately head into the harsh mountains to spur yourself on.</t>
   </si>
   <si>
     <t>jisha_3</t>
   </si>
   <si>
-    <t>「強い人」とは、どんな人だと思う?</t>
-  </si>
-  <si>
-    <t>What do you think it means to be "strong"?</t>
+    <t>忍びとして「強さ」を示すなら?</t>
+  </si>
+  <si>
+    <t>If you were to show "strength" as a shinobi, how would you do it?</t>
   </si>
   <si>
     <t>jisha_3a</t>
   </si>
   <si>
-    <t>人のために、自分を律して行動できる人</t>
-  </si>
-  <si>
-    <t>Someone who can discipline themselves and act for others.</t>
+    <t>数珠を手に、人のために己を律して動く</t>
+  </si>
+  <si>
+    <t>Prayer beads in hand, discipline yourself and act for others.</t>
   </si>
   <si>
     <t>jisha_3b</t>
   </si>
   <si>
-    <t>欲や迷いに振り回されず、静かな心を保てる人</t>
-  </si>
-  <si>
-    <t>Someone who keeps a calm heart, unmoved by desire or doubt.</t>
+    <t>静かな読経で、欲や迷いに振り回されぬ心を示す</t>
+  </si>
+  <si>
+    <t>Show, through quiet chanting, a heart unmoved by desire or doubt.</t>
   </si>
   <si>
     <t>jisha_3c</t>
   </si>
   <si>
-    <t>苦しい状況でも耐え抜き、前に進み続ける人</t>
-  </si>
-  <si>
-    <t>Someone who endures hardship and keeps moving forward.</t>
+    <t>法螺貝を吹き鳴らし、苦しい山道でも前に進み続ける</t>
+  </si>
+  <si>
+    <t>Blow the conch-shell horn and keep pressing on, even up the hardest mountain paths.</t>
   </si>
   <si>
     <t>jisha_3d</t>
   </si>
   <si>
-    <t>自分を鍛え続け、困難に立ち向かえる人</t>
-  </si>
-  <si>
-    <t>Someone who keeps forging themselves and can stand against any difficulty.</t>
+    <t>険しい岩場を歩き通し、鍛え抜いた身体で示す</t>
+  </si>
+  <si>
+    <t>Walk the sheerest cliffs to the end, showing a body forged through training.</t>
   </si>
   <si>
     <t>shomin_1</t>
   </si>
   <si>
-    <t>人前でのお前は?</t>
-  </si>
-  <si>
-    <t>What are you like in front of others?</t>
-  </si>
-  <si>
     <t>shomin_1a</t>
   </si>
   <si>
-    <t>誰の記憶にも残らない、ごく普通の者</t>
-  </si>
-  <si>
-    <t>Utterly unremarkable — no one remembers your face.</t>
+    <t>一般庶民になりきって、紛れ込む</t>
+  </si>
+  <si>
+    <t>Pass yourself off completely as an ordinary commoner and slip in.</t>
   </si>
   <si>
     <t>shomin_1b</t>
   </si>
   <si>
-    <t>商いの話で、自然と人の輪の中心にいる</t>
-  </si>
-  <si>
-    <t>The natural center of attention when trade and dealing is the topic.</t>
+    <t>商いを口実に、堂々と入り込む</t>
+  </si>
+  <si>
+    <t>Use trade as your excuse, and walk in openly.</t>
   </si>
   <si>
     <t>shomin_1c</t>
   </si>
   <si>
-    <t>物静かで、多くを語らない</t>
-  </si>
-  <si>
-    <t>Quiet, and not one to say much.</t>
+    <t>誰にも気づかれず、静かに近づく</t>
+  </si>
+  <si>
+    <t>Approach quietly, unnoticed by anyone.</t>
   </si>
   <si>
     <t>shomin_1d</t>
   </si>
   <si>
-    <t>手品や芸で、人目を引きつける</t>
-  </si>
-  <si>
-    <t>Someone who draws every eye with a trick or a performance.</t>
+    <t>興行の許可を得て、人前で技を披露しながら近づく</t>
+  </si>
+  <si>
+    <t>Get permission to perform, and approach while showing off your skill in front of everyone.</t>
   </si>
   <si>
     <t>shomin_2</t>
   </si>
   <si>
-    <t>お前が得意なのは?</t>
-  </si>
-  <si>
-    <t>What are you good at?</t>
+    <t>忍びとして、お前が得意なのは?</t>
+  </si>
+  <si>
+    <t>As a shinobi, what are you good at?</t>
   </si>
   <si>
     <t>shomin_2a</t>
@@ -1101,16 +1116,16 @@
     <t>shomin_2b</t>
   </si>
   <si>
-    <t>効能を説き、薬を売り歩くこと</t>
-  </si>
-  <si>
-    <t>Talking up remedies and peddling your wares.</t>
+    <t>薬箱を開き、効能を説いて売り歩くこと</t>
+  </si>
+  <si>
+    <t>Opening your medicine chest, talking up its remedies, and peddling them.</t>
   </si>
   <si>
     <t>shomin_2c</t>
   </si>
   <si>
-    <t>気配を殺し、一息で事を成すこと</t>
+    <t>気配を断ち、一息で事を成すこと</t>
   </si>
   <si>
     <t>Erasing your presence and finishing the job in a single breath.</t>
@@ -1119,55 +1134,49 @@
     <t>shomin_2d</t>
   </si>
   <si>
-    <t>別人に成りきり、演じきること</t>
-  </si>
-  <si>
-    <t>Becoming someone else entirely, and playing the part all the way through.</t>
+    <t>面をつけ、別人に成りきり演じきること</t>
+  </si>
+  <si>
+    <t>Putting on a mask, becoming someone else, and playing the part all the way through.</t>
   </si>
   <si>
     <t>shomin_3</t>
   </si>
   <si>
-    <t>人からどう見られたい?</t>
-  </si>
-  <si>
-    <t>How do you want people to see you?</t>
-  </si>
-  <si>
     <t>shomin_3a</t>
   </si>
   <si>
-    <t>特に何とも思われない、当たり前の者として</t>
-  </si>
-  <si>
-    <t>As someone utterly unremarkable, beneath notice.</t>
+    <t>特に何かを究めようとは思わない</t>
+  </si>
+  <si>
+    <t>Nothing in particular — you don't feel the need to master anything.</t>
   </si>
   <si>
     <t>shomin_3b</t>
   </si>
   <si>
-    <t>良い品と良い話をもたらす者として</t>
-  </si>
-  <si>
-    <t>As someone who brings good goods and good stories.</t>
+    <t>物欲を高められるよう、豆知識を増やす</t>
+  </si>
+  <si>
+    <t>Bits of trivia that make people want things more.</t>
   </si>
   <si>
     <t>shomin_3c</t>
   </si>
   <si>
-    <t>何を考えているか分からない者として</t>
-  </si>
-  <si>
-    <t>As someone whose thoughts no one can read.</t>
+    <t>精神統一する</t>
+  </si>
+  <si>
+    <t>Focusing and settling your mind.</t>
   </si>
   <si>
     <t>shomin_3d</t>
   </si>
   <si>
-    <t>笑いと驚きを届ける者として</t>
-  </si>
-  <si>
-    <t>As someone who brings laughter and surprise.</t>
+    <t>人を惹きつける技や、表現の仕方</t>
+  </si>
+  <si>
+    <t>Skills and ways of expressing yourself that draw people in.</t>
   </si>
 </sst>
 </file>
@@ -2575,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2723,6 +2732,39 @@
       </c>
       <c r="C13" s="2" t="s">
         <v>291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2753,167 +2795,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -2944,167 +2986,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>257</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>339</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>368</v>
+        <v>287</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>369</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
